--- a/AAII_Financials/Quarterly/CHTR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHTR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>CHTR</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13526000</v>
+      </c>
+      <c r="E8" s="3">
         <v>13597000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13601000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13672000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13766000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13735000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13926000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13795000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13685000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13679000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13711000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13584000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13659000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13653000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13674000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13550000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13598000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13200000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13212000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>13146000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>12802000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>12522000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>12624000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>12039000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11696000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11738000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11761000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11450000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11347000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11206000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>11231000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10892000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10854000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>10657000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>10602000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>10458000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>10357000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>10164000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>10275000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>10037000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6108000</v>
+      </c>
+      <c r="E9" s="3">
         <v>6080000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5995000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6154000</v>
       </c>
-      <c r="G9" s="3">
-        <v>6146000</v>
-      </c>
       <c r="H9" s="3">
+        <v>6130000</v>
+      </c>
+      <c r="I9" s="3">
         <v>6162000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6221000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6244000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6171000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6364000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6272000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6286000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8305000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8511000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7456000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7386000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7387000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7308000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7140000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7170000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7141000</v>
-      </c>
-      <c r="X9" s="3">
-        <v>6960000</v>
       </c>
       <c r="Y9" s="3">
         <v>6960000</v>
       </c>
       <c r="Z9" s="3">
+        <v>6960000</v>
+      </c>
+      <c r="AA9" s="3">
         <v>6695000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6578000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6666000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5570000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5633000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5468000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5508000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5408000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5272000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>5180000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>6085000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>6076000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>6074000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>5974000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>5997000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>5934000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>5886000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7418000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7517000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7606000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7518000</v>
       </c>
-      <c r="G10" s="3">
-        <v>7620000</v>
-      </c>
       <c r="H10" s="3">
+        <v>7636000</v>
+      </c>
+      <c r="I10" s="3">
         <v>7573000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7705000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7551000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7514000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7315000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7439000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7298000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5354000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5142000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6218000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6164000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6211000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5892000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6072000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5976000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5661000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5562000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5664000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5344000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5118000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5072000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>6191000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5817000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5879000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5698000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5823000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5620000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5674000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4572000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>4526000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>4384000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>4383000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>4167000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>4341000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>4151000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,252 +1467,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="E14" s="3">
         <v>43000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>112000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>147000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>81000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>123000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>73000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>21000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>70000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-38000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-31000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>29000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-58000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>10000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>143000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>250000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-124000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-155000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>71000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>208000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>269000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>62000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>86000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>42000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>43000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>48000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>19000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>23000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>25000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>14000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>35000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>76000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-44000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>147000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>136000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>131000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>203000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>209000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2197000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2211000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2194000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2160000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2176000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2181000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2168000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2145000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2170000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2190000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2188000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2130000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2172000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2206000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2192000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2177000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2240000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2294000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2280000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2270000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2354000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2441000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2409000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2370000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2428000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2497000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2461000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2415000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2500000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>2550000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>2534000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>2482000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>2592000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>2710000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>2742000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>2701000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>2595000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>2550000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>2495000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>2437000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10347000</v>
+      </c>
+      <c r="E17" s="3">
         <v>10350000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10236000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10410000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10406000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10375000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10499000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10437000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10342000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10585000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10699000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10427000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10476000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10715000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10639000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10677000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10310000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10437000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10094000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10297000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10441000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10468000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10184000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9925000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9763000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9963000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9827000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9864000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9806000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9781000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9792000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9512000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9494000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>9615000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>9403000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>9549000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>9306000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>9257000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>9203000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>9126000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3179000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3247000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3365000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3262000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>3360000</v>
       </c>
       <c r="H18" s="3">
         <v>3360000</v>
       </c>
       <c r="I18" s="3">
+        <v>3360000</v>
+      </c>
+      <c r="J18" s="3">
         <v>3427000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3358000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3343000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3094000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3012000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3157000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3183000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2938000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3035000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2873000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3288000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2763000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3118000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2849000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2361000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2054000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2440000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2114000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1933000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1775000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1934000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1586000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1541000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1425000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1439000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1380000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1360000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1042000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1199000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>909000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1051000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>907000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1072000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>911000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,618 +2056,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E20" s="3">
         <v>120000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>22000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>113000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>107000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>142000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>34000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>146000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>95000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>90000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>89000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>17000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>86000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>106000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>14000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>18000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>31000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-26000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-79000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>82000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>66000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>180000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-59000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>66000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-299000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-38000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-30000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-126000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-64000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-167000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>214000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-102000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>60000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>72000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-59000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>42000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>435000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5345000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5338000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5537000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5309000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5429000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5399000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5561000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5357000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5418000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5194000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5111000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5270000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5269000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5038000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5223000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5064000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5546000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5088000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5372000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5040000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4797000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4561000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5029000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4425000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4427000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3973000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4357000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3971000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3915000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3911000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3806000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4076000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3850000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3812000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>4013000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3607000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>3587000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>3499000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>4002000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>3427000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1276000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1256000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1270000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1268000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1263000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1241000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1274000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1311000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1328000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1316000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1319000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1306000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1298000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1265000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1227000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1160000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1109000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1060000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1034000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1016000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1004000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>983000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>965000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>946000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>957000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>980000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>964000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>963000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>945000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>925000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>910000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>901000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>878000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>851000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>840000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>788000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>749000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>713000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>728000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>724000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1999000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1828000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1961000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1734000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1909000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1854000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2046000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1880000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1850000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1726000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1635000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1805000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1857000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1557000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1804000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1727000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2197000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1734000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2058000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1754000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1439000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1137000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1655000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1109000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1042000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>496000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>932000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>593000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>470000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>436000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>362000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>693000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>380000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>251000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>431000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>118000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>243000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>236000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>779000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>266000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>475000</v>
+      </c>
+      <c r="E24" s="3">
         <v>465000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>415000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>418000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>414000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>445000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>370000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>406000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>427000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>446000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>406000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>369000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>444000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>374000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>419000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>360000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>489000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>345000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>224000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>347000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>281000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>216000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>254000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>177000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>166000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>29000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>110000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>126000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>84000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>119000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>109000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>41000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>28000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>114000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>26000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>48000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>25000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>210000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>16000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1524000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1363000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1546000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1316000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1495000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1409000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1676000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1474000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1423000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1280000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1229000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1436000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1413000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1183000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1385000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1367000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1708000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1389000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1834000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1407000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1158000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>921000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1401000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>932000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>876000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>467000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>822000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>467000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>386000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>317000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>360000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>584000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>339000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>223000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>317000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>92000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>195000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>211000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>569000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>250000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1292000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1163000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1332000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1137000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1301000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1217000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1466000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1280000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1231000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1106000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1058000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1255000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1223000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1021000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1196000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1185000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1471000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1203000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1610000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1217000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1020000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>807000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1246000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>814000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>766000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>396000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>714000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>387000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>314000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>253000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>296000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>493000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>273000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>168000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>253000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>48000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>139000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>155000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>454000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3268,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3226,12 +3286,12 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>9300000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-120000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-22000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-113000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-107000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-142000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-34000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-146000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-95000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-90000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-89000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-17000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-86000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-106000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-14000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-18000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-31000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>26000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>79000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-82000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-66000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-180000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>59000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-66000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>299000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>38000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>30000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>126000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>64000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>167000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-214000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>102000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-60000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-72000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>3000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>59000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-42000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-435000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-79000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1292000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1163000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1332000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1137000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1301000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1217000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1466000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1280000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1231000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1106000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1058000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1255000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1223000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1021000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1196000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1185000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1471000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1203000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1610000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1217000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1020000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>807000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1246000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>814000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>766000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>396000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>714000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>387000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>314000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>253000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>296000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>493000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>273000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>168000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>9553000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>48000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>139000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>155000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>454000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1292000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1163000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1332000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1137000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1301000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1217000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1466000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1280000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1231000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1106000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1058000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1255000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1223000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1021000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1196000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1185000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1471000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1203000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1610000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1217000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1020000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>807000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1246000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>814000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>766000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>396000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>714000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>387000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>314000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>253000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>296000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>493000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>273000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>168000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>9553000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>48000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>139000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>155000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>454000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,130 +4276,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>509000</v>
+      </c>
+      <c r="E41" s="3">
         <v>517000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>477000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>464000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>606000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>796000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>459000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>721000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>602000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>661000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>709000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>571000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>478000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>534000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>645000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>480000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>483000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2431000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>601000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>466000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1711000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>772000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>998000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1283000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2097000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2908000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3483000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>508000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>696000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1451000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>551000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>612000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>773000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>576000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>621000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2164000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>694000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2920000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1535000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1165000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4435,130 +4524,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3651000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3510000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3680000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3598000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3549000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3311000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3097000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3067000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3000000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3004000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2965000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2932000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2864000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2851000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2921000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2841000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2779000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2530000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2579000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2645000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2583000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2395000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2201000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2068000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1994000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2091000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2227000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2284000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2070000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1578000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1733000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1736000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1619000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1409000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1635000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1652000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1489000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1311000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1432000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1242000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,8 +4774,11 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4723,252 +4821,258 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>451000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>433000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>476000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>555000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>386000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>387000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>388000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>496000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>707000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>709000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>674000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>760000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>761000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>596000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>574000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>722000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>446000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>381000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>358000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>413000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>299000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>316000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>381000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>435000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>333000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>374000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4973000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4960000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5144000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4867000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4812000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4968000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4233000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4492000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4133000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4396000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4132000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4116000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3929000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4067000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4017000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3754000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3738000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5516000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3566000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3498000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4682000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3663000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3906000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4060000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4765000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5759000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6471000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3388000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3340000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3751000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2730000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2729000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2750000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2398000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2555000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4132000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2564000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4666000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3300000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2781000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>597000</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>518000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>833000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5045,252 +5149,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>47955000</v>
+      </c>
+      <c r="E48" s="3">
         <v>47198000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>47725000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>45187000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>44187000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>43359000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>44157000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>41846000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41256000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>40349000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>40790000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>38617000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>37546000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>36602000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>36039000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>35005000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>34472000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>34173000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>35616000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>35458000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>35494000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>35426000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>35571000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>35353000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>35206000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>35192000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>35683000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>35321000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>35641000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>35960000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>35126000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>34740000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>34411000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>34002000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>33888000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>33300000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>32948000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>32699000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>32963000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>32881000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>97419000</v>
+      </c>
+      <c r="E49" s="3">
         <v>97505000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>98287000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>97733000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>97814000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>97960000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>98867000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>98271000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>98431000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>98573000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>99604000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>99051000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>99290000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>99408000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>99698000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>99999000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>100290000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>100609000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>101825000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>102151000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>102064000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>102471000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>102911000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>103340000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>103785000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>104263000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>104771000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>105285000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>105788000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>106335000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>106914000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>107483000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>108024000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>108625000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>109513000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>110110000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>110762000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>111385000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>112083000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>112527000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3712000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4981000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>581000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3963000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3776000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3690000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>564000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3852000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3937000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3960000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>531000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4351000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4394000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4441000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4769000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4911000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4758000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3650000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1484000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1388000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1786000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1879000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1818000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1440000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1380000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1338000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1263000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1273000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1316000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1211000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1360000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1133000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1066000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1126000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>667000</v>
-      </c>
-      <c r="AL52" s="3">
-        <v>686000</v>
       </c>
       <c r="AM52" s="3">
         <v>686000</v>
       </c>
       <c r="AN52" s="3">
+        <v>686000</v>
+      </c>
+      <c r="AO52" s="3">
         <v>694000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>721000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>708000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>155618000</v>
+      </c>
+      <c r="E54" s="3">
         <v>154644000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>154213000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>152850000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>151589000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>150954000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>150020000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>149371000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>148611000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>148044000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>147193000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>146682000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>145615000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>144870000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>144523000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>143669000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>143258000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>143948000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>142491000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>142495000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>144026000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>143439000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>144206000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>144193000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>145136000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>146552000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>148188000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>145267000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>146085000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>147257000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>146130000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>146085000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>146251000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>146151000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>146623000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>148228000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>146960000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>149444000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>149067000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>148897000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,740 +6116,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1066000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1049000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1034000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>965000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>967000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>929000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>880000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>855000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>832000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>850000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>931000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>771000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>748000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>746000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>952000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>740000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>718000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>706000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>724000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>686000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>704000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>724000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>763000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>728000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>667000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>733000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>786000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>663000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>790000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>661000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>758000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>604000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>732000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>622000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>740000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>572000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>584000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>522000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>454000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>478000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2154000</v>
+      </c>
+      <c r="E58" s="3">
         <v>812000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1943000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1287000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3114000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2393000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2835000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1798000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>2715000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2290000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2292000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2291000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1510000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1522000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1533000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4543000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2997000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2996000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1002000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1005000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1008000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1715000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>706000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4905000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3504000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3516000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1528000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3538000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3290000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3339000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>5387000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3340000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2045000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>2068000</v>
       </c>
-      <c r="AM58" s="3">
-        <v>0</v>
-      </c>
       <c r="AN58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="3">
         <v>2007000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>2028000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>2050000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7977000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7940000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7705000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7867000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7923000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7787000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7198000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7773000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7332000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7653000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6957000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5300000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5190000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5469000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9603000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9333000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9144000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8680000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8737000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8555000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8332000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8187000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8104000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7813000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>7769000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7577000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8095000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7803000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7557000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7751000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8047000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7907000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7905000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7640000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>8305000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>7779000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>7539000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>6991000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>7090000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>6119000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13778000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12375000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13306000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12994000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14556000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13672000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13486000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13160000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10726000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10926000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13214000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12625000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11975000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12242000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12065000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11595000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11395000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13929000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12458000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12237000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10038000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9916000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9875000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10256000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9142000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>13215000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>12385000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>11982000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9875000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>11950000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>12095000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>11850000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>14024000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>11602000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>11090000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>10419000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>8123000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>9520000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>9572000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>8647000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>94556000</v>
+      </c>
+      <c r="E61" s="3">
         <v>96010000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>96620000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>95778000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>93169000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>93164000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>94341000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>94515000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>97565000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>97965000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>96905000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>95800000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>95971000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>95973000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>96093000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>95510000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>94468000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>90679000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>88564000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>85376000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>86962000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>83882000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>81744000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>77947000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>77663000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>74787000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>75636000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>71441000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>71881000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>70665000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>69537000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>69135000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>66730000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>67609000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>68186000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>66064000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>63248000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>60837000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>59719000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>59946000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5146000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5140000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3927000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4886000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4739000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4774000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3641000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4659000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4679000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4581000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3402000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4517000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4660000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4723000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23816000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>24214000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>23882000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>23396000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>23313000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>23356000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>22940000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>22460000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>22306000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>22278000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>21930000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>21828000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>21356000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>21322000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>21235000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>20999000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>20226000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>19872000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>19855000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>19815000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>19816000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>29167000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>29156000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>29183000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>29410000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>29229000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>133717000</v>
+      </c>
+      <c r="E66" s="3">
         <v>133574000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>133694000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>133262000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>131221000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>130432000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>130313000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>131317000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>131897000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>132438000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>132475000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>131938000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>131588000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>131968000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>135404000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>134780000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>133379000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>131888000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>128441000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>125465000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>124684000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>122442000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>120401000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>117287000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>115780000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>116924000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>116743000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>112293000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>110799000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>111523000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>109845000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>108980000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>108808000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>107383000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>107539000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>114999000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>110332000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>109724000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>108928000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>108620000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2938000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-4230000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-5393000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-4095000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-5232000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6533000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7750000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8643000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-9923000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-11154000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-12260000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-11322000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-12577000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-13800000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-14821000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-8816000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-10001000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-11472000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-12675000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2151000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3368000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-4388000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5195000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2016000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1202000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>436000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>40000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3734000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3347000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>3033000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2780000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4828000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4307000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4034000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>3832000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1206000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1158000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1019000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>733000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1007000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16952000</v>
+      </c>
+      <c r="E76" s="3">
         <v>16385000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16054000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15340000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16209000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16247000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15587000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14099000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12879000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11874000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11086000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11098000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10460000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9418000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9119000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8889000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9879000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12060000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14050000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17030000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19342000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>20997000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>23805000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>26906000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>29356000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>29628000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>31445000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>32974000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>35286000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>35734000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>36285000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>37105000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>37443000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>38768000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>39084000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>33229000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>36628000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>39720000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>40139000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>40277000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1292000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1163000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1332000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1137000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1301000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1217000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1466000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1280000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1231000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1106000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1058000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1255000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1223000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1021000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1196000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1185000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1471000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1203000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1610000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1217000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1020000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>807000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1246000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>814000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>766000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>396000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>714000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>387000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>314000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>253000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>296000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>493000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>273000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>168000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>9553000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>48000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>139000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>155000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>454000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2176000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2181000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1330000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2145000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2170000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2190000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1088000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2130000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2172000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2206000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>892000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2177000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2240000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2294000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2192000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2177000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2240000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2294000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2280000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2270000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2354000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2441000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2409000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2370000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2428000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2497000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2461000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2415000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2500000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2550000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2534000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>2482000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>2592000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>2710000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>2742000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>2701000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>2595000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>2550000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>2495000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>2437000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3925000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4304000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3761000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4480000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3600000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4236000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3460000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3905000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3853000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3212000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3855000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3944000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3311000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3323000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3787000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3757000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3734000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3647000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4226000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4263000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3999000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3751000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4149000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3664000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3529000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3220000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3358000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2943000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2761000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2686000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3168000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2804000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3096000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2699000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3258000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>2908000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>2945000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>2843000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3226000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>2801000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2871000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2855000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3335000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3051000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2874000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2399000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3062000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2563000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2853000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2791000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2856000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2961000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2834000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2464000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2920000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2406000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2193000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1857000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2072000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1861000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1881000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1821000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2063000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2014000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1877000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1461000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2282000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1651000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1597000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1665000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2433000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2118000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2391000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2183000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2585000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2393000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-2148000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1555000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1888000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-1748000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3199000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2974000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3038000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3157000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2621000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2804000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2579000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2439000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2729000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2907000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2644000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2894000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2850000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2739000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2768000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2264000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2295000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1787000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1992000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1790000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2016000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1956000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2570000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1986000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1751000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1850000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1854000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1731000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1666000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2080000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2306000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2323000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2369000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2738000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2215000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2328000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1843000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1712000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1385000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1802000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10238,8 +10471,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10316,8 +10549,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,130 +10924,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-749000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1306000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-646000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1451000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1196000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1072000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1125000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1358000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1143000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-353000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1073000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-957000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-517000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-695000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-854000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1496000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3387000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-30000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2099000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3718000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1044000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2024000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1864000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2494000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2612000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1983000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1448000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1461000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1875000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>255000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-757000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-594000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-530000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2586000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>890000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-3328000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>254000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1471000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-389000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E102" s="3">
         <v>24000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>77000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-128000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-217000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>360000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-244000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>108000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-19000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-48000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>138000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>93000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-56000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-111000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>165000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1948000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1830000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>135000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1245000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>939000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-229000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-285000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-816000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-834000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-613000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2952000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-249000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-780000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>861000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>105000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-113000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>197000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-45000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1543000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1470000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-2226000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1385000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>370000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>610000</v>
       </c>
     </row>
